--- a/RR_ISRU.xlsx
+++ b/RR_ISRU.xlsx
@@ -231,7 +231,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="500">
   <si>
     <t>Resource</t>
   </si>
@@ -2137,12 +2137,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2154,6 +2148,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2487,15 +2487,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -2979,15 +2979,15 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
     </row>
     <row r="26" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
@@ -3041,15 +3041,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
       <c r="H1" s="40"/>
       <c r="I1" s="40"/>
     </row>
@@ -3087,7 +3087,7 @@
         <v>72</v>
       </c>
       <c r="B6" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -3115,9 +3115,7 @@
       <c r="A7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>24</v>
-      </c>
+      <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -3130,9 +3128,9 @@
       <c r="A8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="12" t="str">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,4,FALSE),"-")</f>
-        <v>589.29629999999997</v>
+        <v>-</v>
       </c>
       <c r="C8" s="12" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,4,FALSE),"-")</f>
@@ -3167,9 +3165,9 @@
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="12" t="str">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$E$113,5,FALSE),"-")</f>
-        <v>7.8</v>
+        <v>-</v>
       </c>
       <c r="C9" s="12" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$E$113,5,FALSE),"-")</f>
@@ -3206,7 +3204,7 @@
       </c>
       <c r="B10" s="32">
         <f>IFERROR(B6*B8,0)</f>
-        <v>2357.1851999999999</v>
+        <v>0</v>
       </c>
       <c r="C10" s="32" t="str">
         <f>IFERROR(C6*C8,"-")</f>
@@ -3241,9 +3239,9 @@
       <c r="A11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="23" t="str">
         <f t="shared" ref="B11:G11" si="1">IFERROR(B10/(B9*1000),"-")</f>
-        <v>0.30220323076923078</v>
+        <v>-</v>
       </c>
       <c r="C11" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3280,16 +3278,16 @@
       </c>
       <c r="B12" s="15">
         <f>SUM(B10:I10)</f>
-        <v>2357.1851999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="12" t="str">
         <f>IFERROR(VLOOKUP(B7,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>192.86</v>
+        <v>-</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>IFERROR(VLOOKUP(C7,Database!$A$3:$G$113,7,FALSE),"-")</f>
@@ -3323,7 +3321,7 @@
     <row r="15" spans="1:12" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <f>IFERROR(B6*B14,0)</f>
-        <v>771.44</v>
+        <v>0</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" ref="C15:G15" si="3">IFERROR(C6*C14,0)</f>
@@ -3360,7 +3358,7 @@
       </c>
       <c r="B16" s="34">
         <f>SUM(B15:I15)/20</f>
-        <v>38.572000000000003</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1"/>
     </row>
@@ -3383,19 +3381,18 @@
       </c>
       <c r="B20" s="41">
         <f>B6*2</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" s="9">
-        <f>B6*3</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D20" s="9">
         <f>B6*2</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="9">
         <f>B6*10</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -3414,18 +3411,10 @@
       <c r="A21" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
@@ -3435,21 +3424,21 @@
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="12" t="str">
         <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>173.05</v>
-      </c>
-      <c r="C22" s="12">
+        <v>-</v>
+      </c>
+      <c r="C22" s="12" t="str">
         <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>9.01</v>
-      </c>
-      <c r="D22" s="12">
+        <v>-</v>
+      </c>
+      <c r="D22" s="12" t="str">
         <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>28.085000000000001</v>
-      </c>
-      <c r="E22" s="12">
+        <v>-</v>
+      </c>
+      <c r="E22" s="12" t="str">
         <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,4,FALSE),"-")</f>
-        <v>16</v>
+        <v>-</v>
       </c>
       <c r="F22" s="12" t="str">
         <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,4,FALSE),"-")</f>
@@ -3472,21 +3461,21 @@
       <c r="A23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="12" t="str">
         <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>5.2</v>
-      </c>
-      <c r="C23" s="12">
+        <v>-</v>
+      </c>
+      <c r="C23" s="12" t="str">
         <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>0.75080000000000002</v>
-      </c>
-      <c r="D23" s="12">
+        <v>-</v>
+      </c>
+      <c r="D23" s="12" t="str">
         <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>2.3289999999999997</v>
-      </c>
-      <c r="E23" s="12">
+        <v>-</v>
+      </c>
+      <c r="E23" s="12" t="str">
         <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,5,FALSE),"-")</f>
-        <v>1.141</v>
+        <v>-</v>
       </c>
       <c r="F23" s="12" t="str">
         <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,5,FALSE),"-")</f>
@@ -3511,19 +3500,19 @@
       </c>
       <c r="B24" s="10">
         <f>IFERROR(B20*B22,0)</f>
-        <v>1384.4</v>
-      </c>
-      <c r="C24" s="10">
+        <v>0</v>
+      </c>
+      <c r="C24" s="10" t="str">
         <f>IFERROR(C20*C22,"-")</f>
-        <v>108.12</v>
-      </c>
-      <c r="D24" s="10">
+        <v>-</v>
+      </c>
+      <c r="D24" s="10" t="str">
         <f>IFERROR(D20*D22,"-")</f>
-        <v>224.68</v>
-      </c>
-      <c r="E24" s="10">
+        <v>-</v>
+      </c>
+      <c r="E24" s="10" t="str">
         <f>IFERROR(E20*E22,"-")</f>
-        <v>640</v>
+        <v>-</v>
       </c>
       <c r="F24" s="10" t="str">
         <f>IFERROR(F20*F22,"-")</f>
@@ -3546,21 +3535,21 @@
       <c r="A25" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="23" t="str">
         <f t="shared" ref="B25:G25" si="6">IFERROR(B24/(B23*1000),"-")</f>
-        <v>0.26623076923076927</v>
-      </c>
-      <c r="C25" s="23">
+        <v>-</v>
+      </c>
+      <c r="C25" s="23" t="str">
         <f t="shared" si="6"/>
-        <v>0.14400639318060734</v>
-      </c>
-      <c r="D25" s="23">
+        <v>-</v>
+      </c>
+      <c r="D25" s="23" t="str">
         <f t="shared" si="6"/>
-        <v>9.6470588235294141E-2</v>
-      </c>
-      <c r="E25" s="23">
+        <v>-</v>
+      </c>
+      <c r="E25" s="23" t="str">
         <f t="shared" si="6"/>
-        <v>0.56091148115687994</v>
+        <v>-</v>
       </c>
       <c r="F25" s="23" t="str">
         <f t="shared" si="6"/>
@@ -3585,7 +3574,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B24:I24)</f>
-        <v>2357.1999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3595,21 +3584,21 @@
       <c r="A28" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="12" t="str">
         <f>IFERROR(VLOOKUP(B21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>6.25</v>
-      </c>
-      <c r="C28" s="12">
+        <v>-</v>
+      </c>
+      <c r="C28" s="12" t="str">
         <f>IFERROR(VLOOKUP(C21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>9.32</v>
-      </c>
-      <c r="D28" s="12">
+        <v>-</v>
+      </c>
+      <c r="D28" s="12" t="str">
         <f>IFERROR(VLOOKUP(D21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>8.15</v>
-      </c>
-      <c r="E28" s="12">
+        <v>-</v>
+      </c>
+      <c r="E28" s="12" t="str">
         <f>IFERROR(VLOOKUP(E21,Database!$A$3:$G$113,7,FALSE),"-")</f>
-        <v>13.61</v>
+        <v>-</v>
       </c>
       <c r="F28" s="12" t="str">
         <f>IFERROR(VLOOKUP(F21,Database!$A$3:$G$113,7,FALSE),"-")</f>
@@ -3625,19 +3614,19 @@
     <row r="29" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <f>IFERROR(B20*B28,0)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" ref="C29:I29" si="8">IFERROR(C20*C28,0)</f>
-        <v>111.84</v>
+        <v>0</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="8"/>
-        <v>65.2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="10">
         <f t="shared" si="8"/>
-        <v>544.4</v>
+        <v>0</v>
       </c>
       <c r="F29" s="10">
         <f t="shared" si="8"/>
@@ -3662,7 +3651,7 @@
       </c>
       <c r="B30" s="34">
         <f>SUM(B29:I29)/20</f>
-        <v>38.572000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3687,17 +3676,17 @@
       </c>
       <c r="B34" s="11" t="str">
         <f>IF($B$12&gt;$B$26,"Input excesive",IF($B$12&lt;$B$26,"Output excessive","Equal"))</f>
-        <v>Output excessive</v>
+        <v>Equal</v>
       </c>
       <c r="C34" s="22">
         <f>IF($B$12&gt;$B$26,B12/B26,IF($B$12&lt;$B$26,B26/B12,1))</f>
-        <v>1.000006278675091</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D36">
         <f>1/C34</f>
-        <v>0.99999372136433051</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -3786,10 +3775,10 @@
       <c r="C3" s="1">
         <v>0.02</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="50">
         <v>576.85</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="50">
         <f>0.01*1000</f>
         <v>10</v>
       </c>
@@ -3811,10 +3800,10 @@
       <c r="C4" s="1">
         <v>0.8</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="50">
         <v>170.34</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="50">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
@@ -3851,11 +3840,11 @@
       <c r="C5" s="7">
         <v>0.18</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="51">
         <f>54.4</f>
         <v>54.4</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="51">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
@@ -3903,11 +3892,11 @@
       <c r="C6" s="1">
         <v>1.2</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="50">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="50">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
@@ -3955,11 +3944,11 @@
       <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="50">
         <f>131.29</f>
         <v>131.29</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="50">
         <f>0.0001*1000</f>
         <v>0.1</v>
       </c>
@@ -4007,10 +3996,10 @@
       <c r="C8" s="1">
         <v>0.6</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="50">
         <v>1658.174</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="50">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
@@ -4039,11 +4028,11 @@
       <c r="C10" s="1">
         <v>1.35</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="50">
         <f>SUM(($D$51*0.5)+($D$109*0.5))</f>
         <v>46.073</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="50">
         <f>0.0009*1000</f>
         <v>0.9</v>
       </c>
@@ -4067,10 +4056,10 @@
       <c r="C11" s="1">
         <v>0.5</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="50">
         <v>101.96</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="50">
         <f>0.00398*1000</f>
         <v>3.98</v>
       </c>
@@ -4092,10 +4081,10 @@
       <c r="C12" s="1">
         <v>1.5</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="50">
         <v>26.98</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="50">
         <f>0.00277*1000</f>
         <v>2.77</v>
       </c>
@@ -4117,10 +4106,10 @@
       <c r="C13" s="1">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="50">
         <v>17.03</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="50">
         <f>0.000000769*1000</f>
         <v>7.6899999999999994E-4</v>
       </c>
@@ -4142,10 +4131,10 @@
       <c r="C14" s="1">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="D14" s="52">
+      <c r="D14" s="50">
         <v>39.950000000000003</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="50">
         <f>0.000001784*1000</f>
         <v>1.784E-3</v>
       </c>
@@ -4167,10 +4156,10 @@
       <c r="C15" s="1">
         <v>0.5213333</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="50">
         <v>93.13</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="50">
         <f>0.00102*1000</f>
         <v>1.02</v>
       </c>
@@ -4192,16 +4181,16 @@
       <c r="C16" s="24">
         <v>1.4</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="52">
         <v>9.01</v>
       </c>
-      <c r="E16" s="54">
-        <f>0.0007508*1000</f>
-        <v>0.75080000000000002</v>
+      <c r="E16" s="52">
+        <f>0.00185*1000</f>
+        <v>1.85</v>
       </c>
       <c r="F16" s="25">
         <f>D16/(E16 * 1000)</f>
-        <v>1.2000532765050611E-2</v>
+        <v>4.87027027027027E-3</v>
       </c>
       <c r="G16">
         <v>9.32</v>
@@ -4217,10 +4206,10 @@
       <c r="C17" s="24">
         <v>0.8</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="52">
         <v>66.02</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="52">
         <f>0.00244518*1000</f>
         <v>2.4451800000000001</v>
       </c>
@@ -4240,10 +4229,10 @@
         <v>212</v>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="54">
+      <c r="D18" s="52">
         <v>720.6</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="52">
         <f>0.126*1000</f>
         <v>126</v>
       </c>
@@ -4265,10 +4254,10 @@
       <c r="C19" s="7">
         <v>0.85099999999999998</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="51">
         <v>10.81</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="51">
         <f>0.00246*1000</f>
         <v>2.46</v>
       </c>
@@ -4290,10 +4279,10 @@
       <c r="C20" s="7">
         <v>77</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="51">
         <v>132.91</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="51">
         <f>0.00193*1000</f>
         <v>1.9300000000000002</v>
       </c>
@@ -4316,10 +4305,10 @@
       <c r="C21" s="7">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="51">
         <v>40.08</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="51">
         <f>0.00155*1000</f>
         <v>1.55</v>
       </c>
@@ -4342,10 +4331,10 @@
       <c r="C22" s="1">
         <v>0</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="50">
         <v>12.01</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="50">
         <f>0.0021*1000</f>
         <v>2.1</v>
       </c>
@@ -4367,10 +4356,10 @@
       <c r="C23" s="1">
         <v>2.8636999999999998E-6</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="50">
         <v>44.01</v>
       </c>
-      <c r="E23" s="52">
+      <c r="E23" s="50">
         <f>0.000001951*1000</f>
         <v>1.951E-3</v>
       </c>
@@ -4392,10 +4381,10 @@
       <c r="C24" s="1">
         <v>3.32E-6</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="50">
         <v>28.01</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="50">
         <f>0.00000125*1000</f>
         <v>1.25E-3</v>
       </c>
@@ -4417,10 +4406,10 @@
       <c r="C25" s="1">
         <v>16</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="50">
         <v>558.47</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="50">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
@@ -4442,10 +4431,10 @@
       <c r="C26" s="1">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="50">
         <v>35.450000000000003</v>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="50">
         <f>0.0032*1000</f>
         <v>3.2</v>
       </c>
@@ -4465,8 +4454,8 @@
       <c r="C27" s="1">
         <v>15</v>
       </c>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52">
+      <c r="D27" s="50"/>
+      <c r="E27" s="50">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
@@ -4482,10 +4471,10 @@
       <c r="C28" s="1">
         <v>0</v>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="50">
         <v>238.03</v>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="50">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
@@ -4507,10 +4496,10 @@
       <c r="C29" s="1">
         <v>2.7999999999999998E-4</v>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="50">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="50">
         <f>0.00000018*1000</f>
         <v>1.7999999999999998E-4</v>
       </c>
@@ -4532,10 +4521,10 @@
       <c r="C30" s="1">
         <v>4.21</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="50">
         <v>27.67</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="50">
         <f>0.000421*1000</f>
         <v>0.42099999999999999</v>
       </c>
@@ -4557,10 +4546,10 @@
       <c r="C31" s="1">
         <v>0.3</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="50">
         <v>60.08</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="50">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
@@ -4582,10 +4571,10 @@
       <c r="C32" s="1">
         <v>865</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="50">
         <v>238.03</v>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="50">
         <f>0.01097*1000</f>
         <v>10.97</v>
       </c>
@@ -4607,10 +4596,10 @@
       <c r="C33" s="1">
         <v>0.12623999999999999</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="50">
         <v>46.07</v>
       </c>
-      <c r="E33" s="52">
+      <c r="E33" s="50">
         <f>0.000789*1000</f>
         <v>0.78900000000000003</v>
       </c>
@@ -4632,10 +4621,10 @@
       <c r="C34" s="1">
         <v>0.12623999999999999</v>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="50">
         <v>61.206800000000001</v>
       </c>
-      <c r="E34" s="52">
+      <c r="E34" s="50">
         <f>0.00084175*1000</f>
         <v>0.84175</v>
       </c>
@@ -4657,10 +4646,10 @@
       <c r="C35" s="1">
         <v>160</v>
       </c>
-      <c r="D35" s="52">
+      <c r="D35" s="50">
         <v>953.52809999999999</v>
       </c>
-      <c r="E35" s="52">
+      <c r="E35" s="50">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
@@ -4682,10 +4671,10 @@
       <c r="C36" s="1">
         <v>2</v>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="50">
         <v>852.68320000000006</v>
       </c>
-      <c r="E36" s="52">
+      <c r="E36" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
@@ -4707,10 +4696,10 @@
       <c r="C37" s="24">
         <v>920</v>
       </c>
-      <c r="D37" s="54">
+      <c r="D37" s="52">
         <v>412.91</v>
       </c>
-      <c r="E37" s="54">
+      <c r="E37" s="52">
         <f>0.001556*1000</f>
         <v>1.556</v>
       </c>
@@ -4729,10 +4718,10 @@
       <c r="C38" s="24">
         <v>1150</v>
       </c>
-      <c r="D38" s="54">
+      <c r="D38" s="52">
         <v>278.13</v>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="52">
         <f>0.00321*1000</f>
         <v>3.21</v>
       </c>
@@ -4749,8 +4738,8 @@
       <c r="C39" s="1">
         <v>12</v>
       </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52">
+      <c r="D39" s="50"/>
+      <c r="E39" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
@@ -4766,10 +4755,10 @@
       <c r="C40" s="1">
         <v>175</v>
       </c>
-      <c r="D40" s="52">
+      <c r="D40" s="50">
         <v>741.30799999999999</v>
       </c>
-      <c r="E40" s="52">
+      <c r="E40" s="50">
         <f>0.05*1000</f>
         <v>50</v>
       </c>
@@ -4788,10 +4777,10 @@
       <c r="C41" s="1">
         <v>1.0175999999999999E-2</v>
       </c>
-      <c r="D41" s="52">
+      <c r="D41" s="50">
         <v>19</v>
       </c>
-      <c r="E41" s="52">
+      <c r="E41" s="50">
         <f>0.000001696*1000</f>
         <v>1.696E-3</v>
       </c>
@@ -4813,10 +4802,10 @@
       <c r="C42" s="1">
         <v>0.238874700854701</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="50">
         <v>103.14</v>
       </c>
-      <c r="E42" s="52">
+      <c r="E42" s="50">
         <f xml:space="preserve"> 0.00028102905982906*1000</f>
         <v>0.28102905982906001</v>
       </c>
@@ -4838,11 +4827,11 @@
       <c r="C43" s="1">
         <v>150</v>
       </c>
-      <c r="D43" s="52">
+      <c r="D43" s="50">
         <f>5.03</f>
         <v>5.03</v>
       </c>
-      <c r="E43" s="52">
+      <c r="E43" s="50">
         <f>0.000216*1000</f>
         <v>0.216</v>
       </c>
@@ -4861,10 +4850,10 @@
       <c r="C44" s="1">
         <v>2</v>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="50">
         <v>92.09</v>
       </c>
-      <c r="E44" s="52">
+      <c r="E44" s="50">
         <f>0.012*1000</f>
         <v>12</v>
       </c>
@@ -4886,10 +4875,10 @@
       <c r="C45" s="1">
         <v>0.01</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="50">
         <v>172.14</v>
       </c>
-      <c r="E45" s="52">
+      <c r="E45" s="50">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
@@ -4911,10 +4900,10 @@
       <c r="C46" s="1">
         <v>0.11126999999999999</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="50">
         <v>3.016</v>
       </c>
-      <c r="E46" s="52">
+      <c r="E46" s="50">
         <f>0.000000125*1000</f>
         <v>1.25E-4</v>
       </c>
@@ -4936,10 +4925,10 @@
       <c r="C47" s="1">
         <v>9.0999999999999993E-6</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="50">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E47" s="52">
+      <c r="E47" s="50">
         <f>0.0000001786*1000</f>
         <v>1.786E-4</v>
       </c>
@@ -4961,10 +4950,10 @@
       <c r="C48" s="1">
         <v>2.1465000000000001</v>
       </c>
-      <c r="D48" s="52">
+      <c r="D48" s="50">
         <v>34.01</v>
       </c>
-      <c r="E48" s="52">
+      <c r="E48" s="50">
         <f>0.001431*1000</f>
         <v>1.431</v>
       </c>
@@ -4986,10 +4975,10 @@
       <c r="C49" s="1">
         <v>1.8585</v>
       </c>
-      <c r="D49" s="52">
+      <c r="D49" s="50">
         <v>2468.0700000000002</v>
       </c>
-      <c r="E49" s="52">
+      <c r="E49" s="50">
         <f>0.00177*1000</f>
         <v>1.77</v>
       </c>
@@ -5011,10 +5000,10 @@
       <c r="C50" s="1">
         <v>0.5</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="50">
         <v>1009.6214</v>
       </c>
-      <c r="E50" s="52">
+      <c r="E50" s="50">
         <f>0.0015*1000</f>
         <v>1.5</v>
       </c>
@@ -5036,11 +5025,11 @@
       <c r="C51" s="1">
         <v>2.008</v>
       </c>
-      <c r="D51" s="52">
+      <c r="D51" s="50">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
-      <c r="E51" s="52">
+      <c r="E51" s="50">
         <f>0.001004*1000</f>
         <v>1.004</v>
       </c>
@@ -5062,10 +5051,10 @@
       <c r="C52" s="1">
         <v>5.5835999999999999E-5</v>
       </c>
-      <c r="D52" s="52">
+      <c r="D52" s="50">
         <v>1.01</v>
       </c>
-      <c r="E52" s="52">
+      <c r="E52" s="50">
         <f>0.0000000899*1000</f>
         <v>8.9900000000000003E-5</v>
       </c>
@@ -5087,10 +5076,10 @@
       <c r="C53" s="1">
         <v>0.31773000000000001</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="50">
         <v>63.01</v>
       </c>
-      <c r="E53" s="52">
+      <c r="E53" s="50">
         <f>0.001513*1000</f>
         <v>1.5130000000000001</v>
       </c>
@@ -5112,10 +5101,10 @@
       <c r="C54" s="1">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="D54" s="52">
+      <c r="D54" s="50">
         <v>170.34</v>
       </c>
-      <c r="E54" s="52">
+      <c r="E54" s="50">
         <f>0.00082*1000</f>
         <v>0.82</v>
       </c>
@@ -5137,10 +5126,10 @@
       <c r="C55" s="1">
         <v>0.60750000000000004</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="50">
         <v>6.94</v>
       </c>
-      <c r="E55" s="52">
+      <c r="E55" s="50">
         <f>0.000534*1000</f>
         <v>0.53399999999999992</v>
       </c>
@@ -5162,10 +5151,10 @@
       <c r="C56" s="1">
         <v>4</v>
       </c>
-      <c r="D56" s="52">
+      <c r="D56" s="50">
         <v>6.94</v>
       </c>
-      <c r="E56" s="52">
+      <c r="E56" s="50">
         <f>0.000458*1000</f>
         <v>0.45800000000000002</v>
       </c>
@@ -5187,10 +5176,10 @@
       <c r="C57" s="1">
         <v>5</v>
       </c>
-      <c r="D57" s="52">
+      <c r="D57" s="50">
         <v>8.0079999999999991</v>
       </c>
-      <c r="E57" s="52">
+      <c r="E57" s="50">
         <f>0.00082*1000</f>
         <v>0.82</v>
       </c>
@@ -5212,10 +5201,10 @@
       <c r="C58" s="24">
         <v>7</v>
       </c>
-      <c r="D58" s="54">
+      <c r="D58" s="52">
         <v>153.114</v>
       </c>
-      <c r="E58" s="54">
+      <c r="E58" s="52">
         <f>0.0086964*1000</f>
         <v>8.6964000000000006</v>
       </c>
@@ -5237,10 +5226,10 @@
       <c r="C59" s="1">
         <v>0.14199999999999999</v>
       </c>
-      <c r="D59" s="52">
+      <c r="D59" s="50">
         <v>17.03</v>
       </c>
-      <c r="E59" s="52">
+      <c r="E59" s="50">
         <f>0.0007021*1000</f>
         <v>0.70209999999999995</v>
       </c>
@@ -5262,10 +5251,10 @@
       <c r="C60" s="1">
         <v>1.4</v>
       </c>
-      <c r="D60" s="52">
+      <c r="D60" s="50">
         <v>39.950000000000003</v>
       </c>
-      <c r="E60" s="52">
+      <c r="E60" s="50">
         <f>0.0013954*1000</f>
         <v>1.3954</v>
       </c>
@@ -5287,10 +5276,10 @@
       <c r="C61" s="1">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="D61" s="52">
+      <c r="D61" s="50">
         <v>28.01</v>
       </c>
-      <c r="E61" s="52">
+      <c r="E61" s="50">
         <f>0.00079*1000</f>
         <v>0.79</v>
       </c>
@@ -5312,10 +5301,10 @@
       <c r="C62" s="1">
         <v>1.7247E-3</v>
       </c>
-      <c r="D62" s="52">
+      <c r="D62" s="50">
         <v>44.01</v>
       </c>
-      <c r="E62" s="52">
+      <c r="E62" s="50">
         <f>0.00117325*1000</f>
         <v>1.1732500000000001</v>
       </c>
@@ -5337,10 +5326,10 @@
       <c r="C63" s="1">
         <v>0.25600000000000001</v>
       </c>
-      <c r="D63" s="52">
+      <c r="D63" s="50">
         <v>2.0139999999999998</v>
       </c>
-      <c r="E63" s="52">
+      <c r="E63" s="50">
         <f>0.0001624*1000</f>
         <v>0.16239999999999999</v>
       </c>
@@ -5362,10 +5351,10 @@
       <c r="C64" s="1">
         <v>9.0299999999999994</v>
       </c>
-      <c r="D64" s="52">
+      <c r="D64" s="50">
         <v>19</v>
       </c>
-      <c r="E64" s="52">
+      <c r="E64" s="50">
         <f>0.001505*1000</f>
         <v>1.5050000000000001</v>
       </c>
@@ -5387,10 +5376,10 @@
       <c r="C65" s="1">
         <v>52.52</v>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="50">
         <v>3.016</v>
       </c>
-      <c r="E65" s="52">
+      <c r="E65" s="50">
         <f>0.000059*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
@@ -5412,10 +5401,10 @@
       <c r="C66" s="1">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="D66" s="52">
+      <c r="D66" s="50">
         <v>4.0019999999999998</v>
       </c>
-      <c r="E66" s="52">
+      <c r="E66" s="50">
         <f>0.0001786*1000</f>
         <v>0.17860000000000001</v>
       </c>
@@ -5437,10 +5426,10 @@
       <c r="C67" s="1">
         <v>3.6749999999999998E-2</v>
       </c>
-      <c r="D67" s="52">
+      <c r="D67" s="50">
         <v>1.01</v>
       </c>
-      <c r="E67" s="52">
+      <c r="E67" s="50">
         <f>0.00007085*1000</f>
         <v>7.0849999999999996E-2</v>
       </c>
@@ -5460,10 +5449,10 @@
         <v>13</v>
       </c>
       <c r="C68" s="1"/>
-      <c r="D68" s="52">
+      <c r="D68" s="50">
         <v>16.05</v>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="50">
         <f>0.00042561*1000</f>
         <v>0.42560999999999999</v>
       </c>
@@ -5485,10 +5474,10 @@
       <c r="C69" s="1">
         <v>8.2399999999999997E-4</v>
       </c>
-      <c r="D69" s="52">
+      <c r="D69" s="50">
         <v>14.01</v>
       </c>
-      <c r="E69" s="52">
+      <c r="E69" s="50">
         <f>0.000824907*1000</f>
         <v>0.82490700000000006</v>
       </c>
@@ -5510,10 +5499,10 @@
       <c r="C70" s="7">
         <v>4.564E-2</v>
       </c>
-      <c r="D70" s="53">
+      <c r="D70" s="51">
         <v>16</v>
       </c>
-      <c r="E70" s="53">
+      <c r="E70" s="51">
         <f>0.001141*1000</f>
         <v>1.141</v>
       </c>
@@ -5535,10 +5524,10 @@
       <c r="C71" s="1">
         <v>15.8</v>
       </c>
-      <c r="D71" s="52">
+      <c r="D71" s="50">
         <v>570.41099999999994</v>
       </c>
-      <c r="E71" s="52">
+      <c r="E71" s="50">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
@@ -5560,10 +5549,10 @@
       <c r="C72" s="1">
         <v>2</v>
       </c>
-      <c r="D72" s="52">
+      <c r="D72" s="50">
         <v>510.40309999999999</v>
       </c>
-      <c r="E72" s="52">
+      <c r="E72" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
@@ -5585,11 +5574,11 @@
       <c r="C73" s="1">
         <v>1.25</v>
       </c>
-      <c r="D73" s="52">
+      <c r="D73" s="50">
         <f>D67</f>
         <v>1.01</v>
       </c>
-      <c r="E73" s="52">
+      <c r="E73" s="50">
         <f>0.007085*1000</f>
         <v>7.085</v>
       </c>
@@ -5611,10 +5600,10 @@
       <c r="C74" s="1">
         <v>1.76</v>
       </c>
-      <c r="D74" s="52">
+      <c r="D74" s="50">
         <v>159.69</v>
       </c>
-      <c r="E74" s="52">
+      <c r="E74" s="50">
         <f>0.0055*1000</f>
         <v>5.5</v>
       </c>
@@ -5634,10 +5623,10 @@
         <v>119</v>
       </c>
       <c r="C75" s="1"/>
-      <c r="D75" s="52">
+      <c r="D75" s="50">
         <v>159.69</v>
       </c>
-      <c r="E75" s="52">
+      <c r="E75" s="50">
         <f>0.026*1000</f>
         <v>26</v>
       </c>
@@ -5657,11 +5646,11 @@
         <v>413</v>
       </c>
       <c r="C76" s="1"/>
-      <c r="D76" s="52">
+      <c r="D76" s="50">
         <f>55.845</f>
         <v>55.844999999999999</v>
       </c>
-      <c r="E76" s="52">
+      <c r="E76" s="50">
         <f>0.039*1000</f>
         <v>39</v>
       </c>
@@ -5683,11 +5672,11 @@
       <c r="C77" s="1">
         <v>14.24</v>
       </c>
-      <c r="D77" s="52">
+      <c r="D77" s="50">
         <f>55.845</f>
         <v>55.844999999999999</v>
       </c>
-      <c r="E77" s="52">
+      <c r="E77" s="50">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
@@ -5709,11 +5698,11 @@
       <c r="C78" s="1">
         <v>1.8642000000000001E-3</v>
       </c>
-      <c r="D78" s="52">
+      <c r="D78" s="50">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
-      <c r="E78" s="52">
+      <c r="E78" s="50">
         <f>0.000000717*1000</f>
         <v>7.1699999999999997E-4</v>
       </c>
@@ -5735,10 +5724,10 @@
       <c r="C79" s="1">
         <v>0.8</v>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="50">
         <v>910.77710000000002</v>
       </c>
-      <c r="E79" s="52">
+      <c r="E79" s="50">
         <f>0.0027*1000</f>
         <v>2.7</v>
       </c>
@@ -5760,10 +5749,10 @@
       <c r="C80" s="1">
         <v>1.748</v>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="50">
         <v>46.07</v>
       </c>
-      <c r="E80" s="52">
+      <c r="E80" s="50">
         <f>0.00088*1000</f>
         <v>0.88</v>
       </c>
@@ -5783,10 +5772,10 @@
         <v>185</v>
       </c>
       <c r="C81" s="24"/>
-      <c r="D81" s="54">
+      <c r="D81" s="52">
         <v>60.08</v>
       </c>
-      <c r="E81" s="54">
+      <c r="E81" s="52">
         <f>0.00347*1000</f>
         <v>3.47</v>
       </c>
@@ -5808,10 +5797,10 @@
       <c r="C82" s="1">
         <v>0.1</v>
       </c>
-      <c r="D82" s="52">
+      <c r="D82" s="50">
         <v>387.0077</v>
       </c>
-      <c r="E82" s="52">
+      <c r="E82" s="50">
         <f>0.005*1000</f>
         <v>5</v>
       </c>
@@ -5833,10 +5822,10 @@
       <c r="C83" s="1">
         <v>0</v>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="50">
         <v>565.95500000000004</v>
       </c>
-      <c r="E83" s="52">
+      <c r="E83" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
@@ -5858,10 +5847,10 @@
       <c r="C84" s="1">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="D84" s="52">
+      <c r="D84" s="50">
         <v>14.01</v>
       </c>
-      <c r="E84" s="52">
+      <c r="E84" s="50">
         <f>0.000001251*1000</f>
         <v>1.2509999999999999E-3</v>
       </c>
@@ -5883,10 +5872,10 @@
       <c r="C85" s="1">
         <v>0.2175</v>
       </c>
-      <c r="D85" s="52">
+      <c r="D85" s="50">
         <v>92.04</v>
       </c>
-      <c r="E85" s="52">
+      <c r="E85" s="50">
         <f>0.00145*1000</f>
         <v>1.45</v>
       </c>
@@ -5908,10 +5897,10 @@
       <c r="C86" s="1">
         <v>4</v>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="50">
         <v>1004.26</v>
       </c>
-      <c r="E86" s="52">
+      <c r="E86" s="50">
         <f>0.00105*1000</f>
         <v>1.05</v>
       </c>
@@ -5933,10 +5922,10 @@
       <c r="C87" s="1">
         <v>24.06</v>
       </c>
-      <c r="D87" s="52">
+      <c r="D87" s="50">
         <v>104.01</v>
       </c>
-      <c r="E87" s="52">
+      <c r="E87" s="50">
         <f>0.001604*1000</f>
         <v>1.6039999999999999</v>
       </c>
@@ -5956,11 +5945,11 @@
         <v>214</v>
       </c>
       <c r="C88" s="24"/>
-      <c r="D88" s="54">
+      <c r="D88" s="52">
         <f>(14.005*8)+(39.95*6)</f>
         <v>351.74</v>
       </c>
-      <c r="E88" s="54">
+      <c r="E88" s="52">
         <f>0.003310332*1000</f>
         <v>3.3103319999999998</v>
       </c>
@@ -5982,10 +5971,10 @@
       <c r="C89" s="1">
         <v>0.5</v>
       </c>
-      <c r="D89" s="52">
+      <c r="D89" s="50">
         <v>131.16999999999999</v>
       </c>
-      <c r="E89" s="52">
+      <c r="E89" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
@@ -6007,10 +5996,10 @@
       <c r="C90" s="1">
         <v>5.5835999999999999E-5</v>
       </c>
-      <c r="D90" s="52">
+      <c r="D90" s="50">
         <v>16</v>
       </c>
-      <c r="E90" s="52">
+      <c r="E90" s="50">
         <f>0.00000141*1000</f>
         <v>1.41E-3</v>
       </c>
@@ -6032,10 +6021,10 @@
       <c r="C91" s="1">
         <v>6.18</v>
       </c>
-      <c r="D91" s="52">
+      <c r="D91" s="50">
         <v>63.13</v>
       </c>
-      <c r="E91" s="52">
+      <c r="E91" s="50">
         <f>0.000618*1000</f>
         <v>0.61799999999999999</v>
       </c>
@@ -6055,10 +6044,10 @@
         <v>31</v>
       </c>
       <c r="C92" s="1"/>
-      <c r="D92" s="52">
+      <c r="D92" s="50">
         <v>30.97</v>
       </c>
-      <c r="E92" s="55">
+      <c r="E92" s="53">
         <f>$E$4</f>
         <v>5</v>
       </c>
@@ -6078,10 +6067,10 @@
         <v>193</v>
       </c>
       <c r="C93" s="1"/>
-      <c r="D93" s="52">
+      <c r="D93" s="50">
         <v>244</v>
       </c>
-      <c r="E93" s="52">
+      <c r="E93" s="50">
         <f>0.019816*1000</f>
         <v>19.815999999999999</v>
       </c>
@@ -6103,10 +6092,10 @@
       <c r="C94" s="1">
         <v>8</v>
       </c>
-      <c r="D94" s="52">
+      <c r="D94" s="50">
         <v>104.15</v>
       </c>
-      <c r="E94" s="52">
+      <c r="E94" s="50">
         <f>0.00104*1000</f>
         <v>1.0399999999999998</v>
       </c>
@@ -6128,10 +6117,10 @@
       <c r="C95" s="1">
         <v>0.01</v>
       </c>
-      <c r="D95" s="52">
+      <c r="D95" s="50">
         <v>284.77100000000002</v>
       </c>
-      <c r="E95" s="52">
+      <c r="E95" s="50">
         <f>0.00174*1000</f>
         <v>1.74</v>
       </c>
@@ -6153,10 +6142,10 @@
       <c r="C96" s="1">
         <v>140</v>
       </c>
-      <c r="D96" s="52">
+      <c r="D96" s="50">
         <v>589.29629999999997</v>
       </c>
-      <c r="E96" s="52">
+      <c r="E96" s="50">
         <f>0.0078*1000</f>
         <v>7.8</v>
       </c>
@@ -6178,11 +6167,11 @@
       <c r="C97" s="1">
         <v>7</v>
       </c>
-      <c r="D97" s="52">
+      <c r="D97" s="50">
         <f>D25+D77+D94</f>
         <v>718.46500000000003</v>
       </c>
-      <c r="E97" s="52">
+      <c r="E97" s="50">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
@@ -6205,10 +6194,10 @@
       <c r="C98" s="1">
         <v>250</v>
       </c>
-      <c r="D98" s="52">
+      <c r="D98" s="50">
         <v>173.05</v>
       </c>
-      <c r="E98" s="52">
+      <c r="E98" s="50">
         <f>0.0052*1000</f>
         <v>5.2</v>
       </c>
@@ -6230,11 +6219,11 @@
       <c r="C99" s="1">
         <v>1.5</v>
       </c>
-      <c r="D99" s="52">
+      <c r="D99" s="50">
         <f>55.845</f>
         <v>55.844999999999999</v>
       </c>
-      <c r="E99" s="52">
+      <c r="E99" s="50">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
@@ -6254,11 +6243,11 @@
         <v>182</v>
       </c>
       <c r="C100" s="1"/>
-      <c r="D100" s="52">
+      <c r="D100" s="50">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
-      <c r="E100" s="52">
+      <c r="E100" s="50">
         <f>0.004*1000</f>
         <v>4</v>
       </c>
@@ -6280,10 +6269,10 @@
       <c r="C101" s="1">
         <v>0.01</v>
       </c>
-      <c r="D101" s="52">
+      <c r="D101" s="50">
         <v>76.08</v>
       </c>
-      <c r="E101" s="52">
+      <c r="E101" s="50">
         <f>0.0025*1000</f>
         <v>2.5</v>
       </c>
@@ -6305,10 +6294,10 @@
       <c r="C102" s="1">
         <v>0.02</v>
       </c>
-      <c r="D102" s="52">
+      <c r="D102" s="50">
         <v>28.085000000000001</v>
       </c>
-      <c r="E102" s="52">
+      <c r="E102" s="50">
         <f>0.002329*1000</f>
         <v>2.3289999999999997</v>
       </c>
@@ -6330,10 +6319,10 @@
       <c r="C103" s="1">
         <v>32</v>
       </c>
-      <c r="D103" s="52">
+      <c r="D103" s="50">
         <v>481.98500000000001</v>
       </c>
-      <c r="E103" s="52">
+      <c r="E103" s="50">
         <f>0.00378*1000</f>
         <v>3.78</v>
       </c>
@@ -6355,10 +6344,10 @@
       <c r="C104" s="1">
         <v>0.17399999999999999</v>
       </c>
-      <c r="D104" s="52">
+      <c r="D104" s="50">
         <v>186.09</v>
       </c>
-      <c r="E104" s="52">
+      <c r="E104" s="50">
         <f>0.0031*1000</f>
         <v>3.1</v>
       </c>
@@ -6380,10 +6369,10 @@
       <c r="C105" s="1">
         <v>0.3</v>
       </c>
-      <c r="D105" s="52">
+      <c r="D105" s="50">
         <v>483.19</v>
       </c>
-      <c r="E105" s="52">
+      <c r="E105" s="50">
         <f>0.0016*1000</f>
         <v>1.6</v>
       </c>
@@ -6402,10 +6391,10 @@
       <c r="C106" s="1">
         <v>2.5</v>
       </c>
-      <c r="D106" s="52">
+      <c r="D106" s="50">
         <v>516.76</v>
       </c>
-      <c r="E106" s="52">
+      <c r="E106" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
@@ -6427,10 +6416,10 @@
       <c r="C107" s="1">
         <v>46.8</v>
       </c>
-      <c r="D107" s="52">
+      <c r="D107" s="50">
         <v>232.04</v>
       </c>
-      <c r="E107" s="52">
+      <c r="E107" s="50">
         <f>0.0117*1000</f>
         <v>11.700000000000001</v>
       </c>
@@ -6452,10 +6441,10 @@
       <c r="C108" s="1">
         <v>0.7</v>
       </c>
-      <c r="D108" s="52">
+      <c r="D108" s="50">
         <v>270.02999999999997</v>
       </c>
-      <c r="E108" s="52">
+      <c r="E108" s="50">
         <f>0.0075*1000</f>
         <v>7.5</v>
       </c>
@@ -6477,10 +6466,10 @@
       <c r="C109" s="1">
         <v>0.79100000000000004</v>
       </c>
-      <c r="D109" s="52">
+      <c r="D109" s="50">
         <v>60.1</v>
       </c>
-      <c r="E109" s="52">
+      <c r="E109" s="50">
         <f>0.000791*1000</f>
         <v>0.79100000000000004</v>
       </c>
@@ -6502,11 +6491,11 @@
       <c r="C110" s="1">
         <v>8.2899999999999998E-4</v>
       </c>
-      <c r="D110" s="52">
+      <c r="D110" s="50">
         <f>SUM(($D$51*0.25)+($D$109*0.75))</f>
         <v>53.086500000000001</v>
       </c>
-      <c r="E110" s="52">
+      <c r="E110" s="50">
         <f>0.000829*1000</f>
         <v>0.82899999999999996</v>
       </c>
@@ -6529,10 +6518,10 @@
       <c r="C111" s="1">
         <v>0</v>
       </c>
-      <c r="D111" s="52">
+      <c r="D111" s="50">
         <v>565.95500000000004</v>
       </c>
-      <c r="E111" s="52">
+      <c r="E111" s="50">
         <f>0.00075*1000</f>
         <v>0.75</v>
       </c>
@@ -6554,10 +6543,10 @@
       <c r="C112" s="1">
         <v>0</v>
       </c>
-      <c r="D112" s="52">
+      <c r="D112" s="50">
         <v>78.08</v>
       </c>
-      <c r="E112" s="52">
+      <c r="E112" s="50">
         <f>0.001005*1000</f>
         <v>1.0050000000000001</v>
       </c>
@@ -6573,15 +6562,15 @@
       <c r="C113" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="D113" s="52">
+      <c r="D113" s="50">
         <v>18.02</v>
       </c>
-      <c r="E113" s="52">
+      <c r="E113" s="50">
         <f>0.001*1000</f>
         <v>1</v>
       </c>
       <c r="F113" s="8">
-        <f t="shared" ref="F113:F114" si="9">D113/(E113 * 1000)</f>
+        <f t="shared" ref="F113" si="9">D113/(E113 * 1000)</f>
         <v>1.8020000000000001E-2</v>
       </c>
       <c r="G113">
@@ -6594,10 +6583,10 @@
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
-      <c r="D114" s="52">
+      <c r="D114" s="50">
         <v>117.49</v>
       </c>
-      <c r="E114" s="52"/>
+      <c r="E114" s="50"/>
       <c r="F114" s="8" t="str">
         <f>IFERROR(D114/(E114 * 1000),"-")</f>
         <v>-</v>
@@ -6617,7 +6606,7 @@
         <v>83</v>
       </c>
       <c r="D117" s="20"/>
-      <c r="E117" s="52">
+      <c r="E117" s="50">
         <f t="shared" ref="E117:E126" si="10">F117*1000</f>
         <v>5</v>
       </c>
@@ -6629,7 +6618,7 @@
       <c r="A118" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E118" s="52">
+      <c r="E118" s="50">
         <f t="shared" si="10"/>
         <v>19.3</v>
       </c>
@@ -6641,7 +6630,7 @@
       <c r="A119" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E119" s="52">
+      <c r="E119" s="50">
         <f t="shared" si="10"/>
         <v>54.4</v>
       </c>
@@ -6653,7 +6642,7 @@
       <c r="A120" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="E120" s="52">
+      <c r="E120" s="50">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
@@ -6665,7 +6654,7 @@
       <c r="A121" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E121" s="52">
+      <c r="E121" s="50">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
@@ -6677,7 +6666,7 @@
       <c r="A122" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E122" s="52">
+      <c r="E122" s="50">
         <f t="shared" si="10"/>
         <v>0.53399999999999992</v>
       </c>
@@ -6689,7 +6678,7 @@
       <c r="A123" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E123" s="52">
+      <c r="E123" s="50">
         <f t="shared" si="10"/>
         <v>6.0000000000000005E-2</v>
       </c>
@@ -6701,7 +6690,7 @@
       <c r="A124" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E124" s="52">
+      <c r="E124" s="50">
         <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
@@ -6713,7 +6702,7 @@
       <c r="A125" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E125" s="52">
+      <c r="E125" s="50">
         <f t="shared" si="10"/>
         <v>5.0108799999999993</v>
       </c>
@@ -6725,7 +6714,7 @@
       <c r="A126" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E126" s="52">
+      <c r="E126" s="50">
         <f t="shared" si="10"/>
         <v>4.3499999999999996</v>
       </c>
@@ -6737,7 +6726,7 @@
       <c r="A127" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E127" s="52">
+      <c r="E127" s="50">
         <f t="shared" ref="E127:E152" si="11">F127*1000</f>
         <v>6.24</v>
       </c>
@@ -6749,7 +6738,7 @@
       <c r="A128" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E128" s="52">
+      <c r="E128" s="50">
         <f t="shared" si="11"/>
         <v>0.216</v>
       </c>
@@ -6761,7 +6750,7 @@
       <c r="A129" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E129" s="52">
+      <c r="E129" s="50">
         <f t="shared" si="11"/>
         <v>23.125</v>
       </c>
@@ -6773,7 +6762,7 @@
       <c r="A130" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E130" s="52">
+      <c r="E130" s="50">
         <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
@@ -6785,7 +6774,7 @@
       <c r="A131" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E131" s="52">
+      <c r="E131" s="50">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
@@ -6797,7 +6786,7 @@
       <c r="A132" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E132" s="52">
+      <c r="E132" s="50">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -6809,7 +6798,7 @@
       <c r="A133" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E133" s="52">
+      <c r="E133" s="50">
         <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
@@ -6821,7 +6810,7 @@
       <c r="A134" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E134" s="52">
+      <c r="E134" s="50">
         <f t="shared" si="11"/>
         <v>2.4</v>
       </c>
@@ -6833,7 +6822,7 @@
       <c r="A135" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E135" s="52">
+      <c r="E135" s="50">
         <f t="shared" si="11"/>
         <v>13.5</v>
       </c>
@@ -6845,7 +6834,7 @@
       <c r="A136" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E136" s="52">
+      <c r="E136" s="50">
         <f t="shared" si="11"/>
         <v>8.6</v>
       </c>
@@ -6857,7 +6846,7 @@
       <c r="A137" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="E137" s="52">
+      <c r="E137" s="50">
         <f t="shared" si="11"/>
         <v>19.099999999999998</v>
       </c>
@@ -6869,7 +6858,7 @@
       <c r="A138" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E138" s="52">
+      <c r="E138" s="50">
         <f t="shared" si="11"/>
         <v>10.97</v>
       </c>
@@ -6884,7 +6873,7 @@
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="3"/>
-      <c r="E139" s="52">
+      <c r="E139" s="50">
         <f t="shared" si="11"/>
         <v>5.7050000000000001</v>
       </c>
@@ -6899,7 +6888,7 @@
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="3"/>
-      <c r="E140" s="52">
+      <c r="E140" s="50">
         <f t="shared" si="11"/>
         <v>13.5</v>
       </c>
@@ -6914,7 +6903,7 @@
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="3"/>
-      <c r="E141" s="52">
+      <c r="E141" s="50">
         <f t="shared" si="11"/>
         <v>0.35399999999999998</v>
       </c>
@@ -6929,7 +6918,7 @@
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="3"/>
-      <c r="E142" s="52">
+      <c r="E142" s="50">
         <f t="shared" si="11"/>
         <v>2.12805</v>
       </c>
@@ -6944,7 +6933,7 @@
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="3"/>
-      <c r="E143" s="52">
+      <c r="E143" s="50">
         <f t="shared" si="11"/>
         <v>1.08</v>
       </c>
@@ -6959,7 +6948,7 @@
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="3"/>
-      <c r="E144" s="52">
+      <c r="E144" s="50">
         <f t="shared" si="11"/>
         <v>4.1000000000000005</v>
       </c>
@@ -6971,7 +6960,7 @@
       <c r="A145" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E145" s="52">
+      <c r="E145" s="50">
         <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
@@ -6983,7 +6972,7 @@
       <c r="A146" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E146" s="52">
+      <c r="E146" s="50">
         <f t="shared" si="11"/>
         <v>4.5999999999999996</v>
       </c>
@@ -6995,7 +6984,7 @@
       <c r="A147" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E147" s="52">
+      <c r="E147" s="50">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -7007,7 +6996,7 @@
       <c r="A148" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E148" s="52">
+      <c r="E148" s="50">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -7019,7 +7008,7 @@
       <c r="A149" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E149" s="52">
+      <c r="E149" s="50">
         <f t="shared" si="11"/>
         <v>7.5</v>
       </c>
@@ -7031,7 +7020,7 @@
       <c r="A150" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E150" s="52">
+      <c r="E150" s="50">
         <f t="shared" si="11"/>
         <v>4.3499999999999996</v>
       </c>
@@ -7043,7 +7032,7 @@
       <c r="A151" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="E151" s="52">
+      <c r="E151" s="50">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
@@ -7055,7 +7044,7 @@
       <c r="A152" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E152" s="52">
+      <c r="E152" s="50">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
